--- a/dreame_sav/Doc_calibration/Calibration_procedures_TEMPLATE.xlsx
+++ b/dreame_sav/Doc_calibration/Calibration_procedures_TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://groupefnac-my.sharepoint.com/personal/jerome_leconte_fnacdarty_com/Documents/Documents/Claude/Projects/HUB Drive constructeurs/dreame_sav/Doc_calibration/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_77B3CBBCE68BFE486A5E39A1AD3234F9D01D1B08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5801EFAA-B2DE-4014-8010-8C9EC85C92AB}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_77B3CBBCE68BFE486A5E39A1AD3234F9D01D1B08" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{654DCD48-7DB9-48B5-91AB-32037EA5F2C7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -157,13 +157,132 @@
 Etape 3 : Calibration du laser linéaire</t>
   </si>
   <si>
+    <t>Pour l’étalonnage de l’IA et le calibrage en damier, le fonctionnement est le même que pour X40 ;
+**[[orange]]Pour l’étalonnage du laser linéaire, l’étalonnage des robots LDS de levage doit être effectuée à une distance de **25 cm (photo 2)** d’un mur blanc pour les autres modèles à une distance de **1 mètre**[[/]]**
+**Suivant les modèles le robot peut rester immobile ou avancer lentement.**</t>
+  </si>
+  <si>
+    <t>Notification technique - Aspirateur robot - Calibrage du plan lumineux
+Calibrage du plan lumineux
+Pour améliorer le taux de réussite du calibrage du plan optique, veuillez configurer une source de lumière LED et éclairer un mur blanc pendant le calibrage. Avec un éclairage suffisant, vous pouvez placer la machine à une distance de 50 cm ; la machine pourra toujours effectuer le calibrage à cette distance.
+[[orange]]Pour les machines LDS de levage, vous pouvez également configurer une source de lumière LED et calibrer à une distance de 25 cm pour améliorer le taux de réussite du calibrage[[/}}. **(photo 3)**</t>
+  </si>
+  <si>
+    <t>Calibration double caméra</t>
+  </si>
+  <si>
+    <t>Calibration_double_camera_1.png ; Calibration_double_camera_2.png ; Calibration_double_camera_3.png ; https://vimeo.com/1200505157 ; https://vimeo.com/1209428006 ;</t>
+  </si>
+  <si>
+    <t>Pairing (Base station-Robot)</t>
+  </si>
+  <si>
+    <t>Tof Cliff Sensor Calibration / Capteur falaise TOF / Capteur de vide</t>
+  </si>
+  <si>
+    <t>Tof_Cliff_Sensor_1.png ; Tof_Cliff_Sensor_2.png ; Tof_Cliff_Sensor_3.png ; Tof_Cliff_Sensor_4.png ;</t>
+  </si>
+  <si>
+    <t>Edge tof Calibration (Calibration du capteur de bord)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. **Xtalk :** Avant de calibrer le xtalk, assurez-vous qu'il n'y a aucun obstacle dans un **rayon de 60 cm Figure 1** autour du capteur de bord situé sur le côté droit du robot. Après la calibration, la réussite s'affiche **(en cas d'échec, l'offset ne peut pas être calibré)**, et le bouton offset ci-dessous s'allume **(sur certains modèles, les deux boutons s'allument)**. 
+2. **offset :** Placez le robot contre un mur perpendiculaire au sol comme illustré à la **Figure 2**. Cliquez sur calibration offset. Veuillez prêter une attention particulière à la distance, sinon la distance de bord risque d'être anormale. Une fois la calibration terminée, veuillez effectuer un test.
+</t>
+  </si>
+  <si>
+    <t>Edge_calibration_1.png ; Edge_calibration_2.png ; Edge_calibration_3.png ;</t>
+  </si>
+  <si>
+    <t>Attention particularité Pour les **Matrix10 Ultra**</t>
+  </si>
+  <si>
+    <t>1. Après avoir remplacé la carte mère ou les moteurs du robot (moteur de brosse latérale, moteur de brosse rotative, soufflante, moteur de serpillière, pompe à eau du robot, etc.), vous devez effectuer une calibration du courant pour vous assurer que les moteurs fonctionnent correctement.
+2. Si le robot ne fonctionne toujours pas après le remplacement d'un composant électronique, essayez d'effectuer une calibration du courant pour diagnostiquer le problème.</t>
+  </si>
+  <si>
+    <t>**Méthode 1 :**
+Applicable aux nouveaux modèles, y compris les modèles postérieurs au X40 : vous pouvez effectuer la calibration du courant dans l'APPLICATION ;
+**Méthode 2 :**
+Pour les modèles plus anciens, vous devez utiliser l'outil de port série et le logiciel PC</t>
+  </si>
+  <si>
+    <t>Current_Calibration_1.png ; Current_Calibration_2.png ;</t>
+  </si>
+  <si>
+    <t>Après une attente de **15 secondes**, le courant du robot sera réinitialisé</t>
+  </si>
+  <si>
+    <t>Wifi Station Infrared Pairing</t>
+  </si>
+  <si>
+    <t>Appairage de la station de base et du robot ; Matrix10 Ultra, MOVA MOBIUS 60
+L'appairage est nécessaire après le remplacement de la carte mère du robot ou de la carte mère de la station de base.</t>
+  </si>
+  <si>
+    <t>Vous devez placer le robot dans la station de base et cliquer sur Appairer. Assurez-vous qu'aucune autre station de base ne se trouve à proximité afin d'éviter les interférences de signal.
+Une fois l'appairage terminé, testez les fonctions de la station de base, comme le nettoyage de la serpillière, pour vous assurer qu'elles fonctionnent correctement.</t>
+  </si>
+  <si>
+    <t>Wifi_Station_Infrared_Pairing_1.png ;</t>
+  </si>
+  <si>
+    <t>**Remarque 1 :** Ces deux modèles sont conçus pour le remplacement automatique de la serpillière ; le robot et la station de base doivent être appairés en 1 pour 1. 
+- La fonction de la station de base utilise un appairage WIFI. Le module WIFI se trouve sur la carte principale et sur la carte de commande de la station de base et nécessite une adresse MAC appairée en 1 pour 1. Sans appairage, la fonction de station de base ne peut pas être utilisée.
+**Remarque 2 :** La recharge est possible sans appairage, et le robot peut aussi être rechargé avec une autre station de base ;
+- La recharge repose sur un signal infrarouge, à partir des signaux émis par la carte de commande de recharge infrarouge du robot et de la station de base. Le signal de recharge des modèles Matrix10 Ultra et MOVA MOBIUS 60 est identique et permet la recharge avec plusieurs stations de base ;</t>
+  </si>
+  <si>
+    <t>Mode d'emploi du gabarit</t>
+  </si>
+  <si>
+    <t>• Type de calibrage : NE PAS modifier les libellés — ils servent de clé de liaison avec Calibration tips.xlsx.</t>
+  </si>
+  <si>
+    <t>• Accès : où trouver le calibrage dans l'application / le chemin de menu.</t>
+  </si>
+  <si>
+    <t>• Action : la manip principale (cliquer sur un bouton, prendre une photo de la mire, lancer un script…).</t>
+  </si>
+  <si>
+    <t>• Étapes détaillées : le déroulé pas à pas.</t>
+  </si>
+  <si>
+    <t>• Captures écran associées : le NOM des fichiers image, séparés par « ; ». Range les images dans un dossier dédié.</t>
+  </si>
+  <si>
+    <t>• Remarques : précautions, cas particuliers, durée, etc.</t>
+  </si>
+  <si>
+    <t>Astuce : garde ce fichier + un dossier « captures » côte à côte. Je relie ensuite ce fichier au fichier Tips dans l'onglet Calibrage.</t>
+  </si>
+  <si>
+    <t>1. Placez le robot sur l'outil de calibration en damier, cliquez sur **« unical calibration »**, puis sur **« camera-extrinsic-calib »**, et attendez l'apparition de [[vert]]**« PASS »[[/]]**, qui indique la réussite de la calibration des paramètres intrinsèques et extrinsèques. Comme illustré sur la **figure 1**
+2. Placez le robot sur le support de calibration double caméra, à une distance de **19 cm** du support. La hauteur de placement du robot doit être alignée avec le bas des deux lignes blanches de la grille situées sous le point noir au centre du robot. Comme illustré sur la **figure 2**
+3. Cliquez sur **« stereo-rectify »** et attendez l'apparition de [[vert]]**« PASS »[[/]]**, qui indique la réussite de la calibration double caméra. Comme illustré sur la **figure 3**</t>
+  </si>
+  <si>
+    <t>1 - Accéder à **l'interface de calibration** via l'app de diagnostic.
+2 - **Retourner le robot**, s'assurer qu'il n'y a pas d'obstruction à **60 cm au-dessus** du capteur TOF.
+3 - Cliquer sur **« Calibration xtalk »** et attendre **[[vert]]« Réussi »[[/]]**.
+4 - Placer sur **surface blanche**, cliquer **« Calibration Offset 1 »**. Le robot soulève ses roues. Attendre [[vert]]**« Réussi »[[/]]**.</t>
+  </si>
+  <si>
+    <t>Current Calibration **(Suite changement tout type de moteur)**</t>
+  </si>
+  <si>
+    <t>Pour garantir un bon fonctionnement après le remplacement du capteur de vide ToF avant, vous devez calibrer le capteur de vide ToF avant. 
+[[vert]]**Les deux capteurs de vide à l'avant de la machine sont noirs, ce qui indique que ce modèle est équipé de capteurs de vide ToF[[/]]**; l[[bleu]]**es capteurs de vide transparents ne nécessitent pas de calibration[[/}]]** ;
+Modèles avec capteurs de vide ToF : X50 Ultra Complete, X50 Master, série Aqua10</t>
+  </si>
+  <si>
     <t xml:space="preserve">## Étape 1 : AI calibration
 1. Cliquez sur l'option de calibration des capteurs à la Figure 1 pour accéder à l'interface de calibration des capteurs, où vous pouvez voir la calibration IA ;
 2. Placez le robot sur l'outil de calibration comme illustré à la Figure 2, assurez-vous que la roue principale du robot est bien placée dans la rainure de positionnement de l'outil, et que le robot n'est pas incliné ;
 3 - Cliquez sur la commande « AI Calibration » comme illustré à la Figure 3 pour lancer la calibration ;
 4 - Déterminez si une recalibration est nécessaire en fonction du résultat affiché ;
  ◻ Si la calibration réussit, « Calibration completed, ok » s'affiche, comme illustré à la Figure 4               
- ◻ En cas d'échec, « Calibration failed, Fail » s'affiche
+ ◻ En cas d'échec, [[rouge]]**« Calibration failed, Fail »[[/]]** s'affiche
 img: AI Calibration_1.png
 ## Étape 2 : Calibration du laser linéaire (Vérification calibration damier)
 1- Cliquez sur l'option de calibration du module laser linéaire à la Figure 1 pour accéder à l'interface de calibration du module laser linéaire, où vous pouvez voir « checkerboard calibration » ;
@@ -183,125 +302,6 @@
 5 - **[[vert]]**Si les étapes ci-dessus réussissent[[/]]**, cela signifie que la calibration du laser linéaire est terminée.
 img: Line_laser_Calibration_1.png ; Line_laser_Calibration_2.png
 </t>
-  </si>
-  <si>
-    <t>Pour l’étalonnage de l’IA et le calibrage en damier, le fonctionnement est le même que pour X40 ;
-**[[orange]]Pour l’étalonnage du laser linéaire, l’étalonnage des robots LDS de levage doit être effectuée à une distance de **25 cm (photo 2)** d’un mur blanc pour les autres modèles à une distance de **1 mètre**[[/]]**
-**Suivant les modèles le robot peut rester immobile ou avancer lentement.**</t>
-  </si>
-  <si>
-    <t>Notification technique - Aspirateur robot - Calibrage du plan lumineux
-Calibrage du plan lumineux
-Pour améliorer le taux de réussite du calibrage du plan optique, veuillez configurer une source de lumière LED et éclairer un mur blanc pendant le calibrage. Avec un éclairage suffisant, vous pouvez placer la machine à une distance de 50 cm ; la machine pourra toujours effectuer le calibrage à cette distance.
-[[orange]]Pour les machines LDS de levage, vous pouvez également configurer une source de lumière LED et calibrer à une distance de 25 cm pour améliorer le taux de réussite du calibrage[[/}}. **(photo 3)**</t>
-  </si>
-  <si>
-    <t>Calibration double caméra</t>
-  </si>
-  <si>
-    <t>Calibration_double_camera_1.png ; Calibration_double_camera_2.png ; Calibration_double_camera_3.png ; https://vimeo.com/1200505157 ; https://vimeo.com/1209428006 ;</t>
-  </si>
-  <si>
-    <t>Pairing (Base station-Robot)</t>
-  </si>
-  <si>
-    <t>Tof Cliff Sensor Calibration / Capteur falaise TOF / Capteur de vide</t>
-  </si>
-  <si>
-    <t>Tof_Cliff_Sensor_1.png ; Tof_Cliff_Sensor_2.png ; Tof_Cliff_Sensor_3.png ; Tof_Cliff_Sensor_4.png ;</t>
-  </si>
-  <si>
-    <t>Pour garantir un bon fonctionnement après le remplacement du capteur de vide ToF avant, vous devez calibrer le capteur de vide ToF avant. 
-Les deux capteurs de vide à l'avant de la machine sont noirs, ce qui indique que ce modèle est équipé de capteurs de vide ToF ; les capteurs de vide transparents ne nécessitent pas de calibration ;
-Modèles avec capteurs de vide ToF : X50 Ultra Complete, X50 Master, série Aqua10</t>
-  </si>
-  <si>
-    <t>Edge tof Calibration (Calibration du capteur de bord)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. **Xtalk :** Avant de calibrer le xtalk, assurez-vous qu'il n'y a aucun obstacle dans un **rayon de 60 cm Figure 1** autour du capteur de bord situé sur le côté droit du robot. Après la calibration, la réussite s'affiche **(en cas d'échec, l'offset ne peut pas être calibré)**, et le bouton offset ci-dessous s'allume **(sur certains modèles, les deux boutons s'allument)**. 
-2. **offset :** Placez le robot contre un mur perpendiculaire au sol comme illustré à la **Figure 2**. Cliquez sur calibration offset. Veuillez prêter une attention particulière à la distance, sinon la distance de bord risque d'être anormale. Une fois la calibration terminée, veuillez effectuer un test.
-</t>
-  </si>
-  <si>
-    <t>Edge_calibration_1.png ; Edge_calibration_2.png ; Edge_calibration_3.png ;</t>
-  </si>
-  <si>
-    <t>Attention particularité Pour les **Matrix10 Ultra**</t>
-  </si>
-  <si>
-    <t>1. Après avoir remplacé la carte mère ou les moteurs du robot (moteur de brosse latérale, moteur de brosse rotative, soufflante, moteur de serpillière, pompe à eau du robot, etc.), vous devez effectuer une calibration du courant pour vous assurer que les moteurs fonctionnent correctement.
-2. Si le robot ne fonctionne toujours pas après le remplacement d'un composant électronique, essayez d'effectuer une calibration du courant pour diagnostiquer le problème.</t>
-  </si>
-  <si>
-    <t>**Méthode 1 :**
-Applicable aux nouveaux modèles, y compris les modèles postérieurs au X40 : vous pouvez effectuer la calibration du courant dans l'APPLICATION ;
-**Méthode 2 :**
-Pour les modèles plus anciens, vous devez utiliser l'outil de port série et le logiciel PC</t>
-  </si>
-  <si>
-    <t>Current_Calibration_1.png ; Current_Calibration_2.png ;</t>
-  </si>
-  <si>
-    <t>Après une attente de **15 secondes**, le courant du robot sera réinitialisé</t>
-  </si>
-  <si>
-    <t>Wifi Station Infrared Pairing</t>
-  </si>
-  <si>
-    <t>Appairage de la station de base et du robot ; Matrix10 Ultra, MOVA MOBIUS 60
-L'appairage est nécessaire après le remplacement de la carte mère du robot ou de la carte mère de la station de base.</t>
-  </si>
-  <si>
-    <t>Vous devez placer le robot dans la station de base et cliquer sur Appairer. Assurez-vous qu'aucune autre station de base ne se trouve à proximité afin d'éviter les interférences de signal.
-Une fois l'appairage terminé, testez les fonctions de la station de base, comme le nettoyage de la serpillière, pour vous assurer qu'elles fonctionnent correctement.</t>
-  </si>
-  <si>
-    <t>Wifi_Station_Infrared_Pairing_1.png ;</t>
-  </si>
-  <si>
-    <t>**Remarque 1 :** Ces deux modèles sont conçus pour le remplacement automatique de la serpillière ; le robot et la station de base doivent être appairés en 1 pour 1. 
-- La fonction de la station de base utilise un appairage WIFI. Le module WIFI se trouve sur la carte principale et sur la carte de commande de la station de base et nécessite une adresse MAC appairée en 1 pour 1. Sans appairage, la fonction de station de base ne peut pas être utilisée.
-**Remarque 2 :** La recharge est possible sans appairage, et le robot peut aussi être rechargé avec une autre station de base ;
-- La recharge repose sur un signal infrarouge, à partir des signaux émis par la carte de commande de recharge infrarouge du robot et de la station de base. Le signal de recharge des modèles Matrix10 Ultra et MOVA MOBIUS 60 est identique et permet la recharge avec plusieurs stations de base ;</t>
-  </si>
-  <si>
-    <t>Mode d'emploi du gabarit</t>
-  </si>
-  <si>
-    <t>• Type de calibrage : NE PAS modifier les libellés — ils servent de clé de liaison avec Calibration tips.xlsx.</t>
-  </si>
-  <si>
-    <t>• Accès : où trouver le calibrage dans l'application / le chemin de menu.</t>
-  </si>
-  <si>
-    <t>• Action : la manip principale (cliquer sur un bouton, prendre une photo de la mire, lancer un script…).</t>
-  </si>
-  <si>
-    <t>• Étapes détaillées : le déroulé pas à pas.</t>
-  </si>
-  <si>
-    <t>• Captures écran associées : le NOM des fichiers image, séparés par « ; ». Range les images dans un dossier dédié.</t>
-  </si>
-  <si>
-    <t>• Remarques : précautions, cas particuliers, durée, etc.</t>
-  </si>
-  <si>
-    <t>Astuce : garde ce fichier + un dossier « captures » côte à côte. Je relie ensuite ce fichier au fichier Tips dans l'onglet Calibrage.</t>
-  </si>
-  <si>
-    <t>1. Placez le robot sur l'outil de calibration en damier, cliquez sur **« unical calibration »**, puis sur **« camera-extrinsic-calib »**, et attendez l'apparition de [[vert]]**« PASS »[[/]]**, qui indique la réussite de la calibration des paramètres intrinsèques et extrinsèques. Comme illustré sur la **figure 1**
-2. Placez le robot sur le support de calibration double caméra, à une distance de **19 cm** du support. La hauteur de placement du robot doit être alignée avec le bas des deux lignes blanches de la grille situées sous le point noir au centre du robot. Comme illustré sur la **figure 2**
-3. Cliquez sur **« stereo-rectify »** et attendez l'apparition de [[vert]]**« PASS »[[/]]**, qui indique la réussite de la calibration double caméra. Comme illustré sur la **figure 3**</t>
-  </si>
-  <si>
-    <t>1 - Accéder à **l'interface de calibration** via l'app de diagnostic.
-2 - **Retourner le robot**, s'assurer qu'il n'y a pas d'obstruction à **60 cm au-dessus** du capteur TOF.
-3 - Cliquer sur **« Calibration xtalk »** et attendre **[[vert]]« Réussi »[[/]]**.
-4 - Placer sur **surface blanche**, cliquer **« Calibration Offset 1 »**. Le robot soulève ses roues. Attendre [[vert]]**« Réussi »[[/]]**.</t>
-  </si>
-  <si>
-    <t>Current Calibration **(Suite changement tout type de moteur)**</t>
   </si>
 </sst>
 </file>
@@ -943,34 +943,34 @@
         <v>28</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E9" s="18"/>
       <c r="F9" s="14" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="132" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="19" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B10" s="16" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F10" s="3"/>
     </row>
     <row r="11" spans="1:6" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5"/>
@@ -980,70 +980,70 @@
     </row>
     <row r="12" spans="1:6" ht="118.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="19" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="16" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="5"/>
       <c r="E13" s="14" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="70.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="F14" s="16" t="s">
         <v>43</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="273.60000000000002" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F15" s="20" t="s">
         <v>48</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1070,7 +1070,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -1078,32 +1078,32 @@
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6" s="7" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.3">
@@ -1111,7 +1111,7 @@
     </row>
     <row r="10" spans="1:1" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
